--- a/Test Case/CAB_Test_Cases.xlsx
+++ b/Test Case/CAB_Test_Cases.xlsx
@@ -2,10 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mô tả các cột" sheetId="1" r:id="R2fef6d7cfb624de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FR Test Cases" sheetId="2" r:id="R01a42a7dae524430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FR Traceability" sheetId="3" r:id="Rab0404d5e8a040ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nguồn &amp; phạm vi" sheetId="4" r:id="Rd8d72a72c02e4321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mô tả các cột" sheetId="1" r:id="Rb31e733887fd42f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FR Test Cases" sheetId="2" r:id="Re39a7d5999564a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FR Traceability" sheetId="3" r:id="Rc3854ea30f804719"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -123,7 +122,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FRCasesTable" displayName="FRCasesTable" ref="A1:H51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FRCases30Table" displayName="FRCases30Table" ref="A1:H31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Test Case ID"/>
     <x:tableColumn id="2" name="Test Scenario"/>
@@ -139,7 +138,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FRTraceabilityTable" displayName="FRTraceabilityTable" ref="A1:E40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FRTraceability30Table" displayName="FRTraceability30Table" ref="A1:E40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="FR Code"/>
     <x:tableColumn id="2" name="Functional Requirement"/>
@@ -491,11 +490,11 @@
   <x:cols>
     <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="37" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -525,1310 +524,790 @@
         <x:v>Priority</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="54" customHeight="1">
+    <x:row r="2" ht="60" customHeight="1">
       <x:c r="A2" s="12" t="str">
         <x:v>TC-CAB-001</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
-        <x:v>Nhập điểm đón</x:v>
+        <x:v>Thông tin đặt chuyến</x:v>
       </x:c>
       <x:c r="C2" s="12" t="str">
-        <x:v>Nhập điểm đón hợp lệ</x:v>
+        <x:v>Nhập đầy đủ điểm đón, điểm đến và loại xe</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>Màn hình đặt chuyến đang mở</x:v>
+        <x:v>Mở màn hình đặt chuyến</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
-        <x:v>Nhập điểm đón hợp lệ</x:v>
+        <x:v>Nhập điểm đón; nhập điểm đến; chọn loại xe</x:v>
       </x:c>
       <x:c r="F2" s="12" t="str">
-        <x:v>Điểm đón: 1 Lê Lợi, Q.1</x:v>
+        <x:v>Điểm đón: 1 Lê Lợi; Điểm đến: 2 Nguyễn Huệ; Xe: 4 chỗ</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Hệ thống ghi nhận điểm đón để tiếp tục đặt chuyến</x:v>
+        <x:v>Hệ thống ghi nhận đầy đủ thông tin chuyến</x:v>
       </x:c>
       <x:c r="H2" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="54" customHeight="1">
+    <x:row r="3" ht="60" customHeight="1">
       <x:c r="A3" s="12" t="str">
         <x:v>TC-CAB-002</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>Nhập điểm đến</x:v>
+        <x:v>Thông tin đặt chuyến</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
-        <x:v>Nhập điểm đến hợp lệ</x:v>
+        <x:v>Không cho đặt chuyến khi thiếu hoặc sai thông tin</x:v>
       </x:c>
       <x:c r="D3" s="12" t="str">
-        <x:v>Màn hình đặt chuyến đang mở</x:v>
+        <x:v>Mở màn hình đặt chuyến</x:v>
       </x:c>
       <x:c r="E3" s="12" t="str">
-        <x:v>Nhập điểm đến hợp lệ</x:v>
+        <x:v>Để trống hoặc nhập sai một trường bắt buộc; nhấn Đặt xe</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
-        <x:v>Điểm đến: 2 Nguyễn Huệ, Q.1</x:v>
+        <x:v>Điểm đón: trống</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Hệ thống ghi nhận điểm đến để tiếp tục đặt chuyến</x:v>
+        <x:v>Hiển thị lỗi đúng trường và không tạo yêu cầu chuyến</x:v>
       </x:c>
       <x:c r="H3" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="54" customHeight="1">
+    <x:row r="4" ht="60" customHeight="1">
       <x:c r="A4" s="12" t="str">
         <x:v>TC-CAB-003</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>Chọn loại xe</x:v>
+        <x:v>Gửi yêu cầu đặt chuyến</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
-        <x:v>Chọn loại xe trước khi đặt chuyến</x:v>
+        <x:v>Tạo yêu cầu đặt xe hợp lệ</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
-        <x:v>Đã nhập điểm đón và điểm đến</x:v>
+        <x:v>Đã nhập đủ thông tin chuyến hợp lệ</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
-        <x:v>Chọn một loại xe</x:v>
+        <x:v>Nhấn Đặt xe</x:v>
       </x:c>
       <x:c r="F4" s="12" t="str">
-        <x:v>Loại xe: 4 chỗ</x:v>
+        <x:v>Chuyến xe 4 chỗ hợp lệ</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Hệ thống ghi nhận loại xe đã chọn</x:v>
+        <x:v>Hệ thống tạo, lưu yêu cầu và thông báo đã tiếp nhận cho khách hàng</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="54" customHeight="1">
+    <x:row r="5" ht="60" customHeight="1">
       <x:c r="A5" s="12" t="str">
         <x:v>TC-CAB-004</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Gửi yêu cầu đặt chuyến</x:v>
+        <x:v>Tìm tài xế</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
-        <x:v>Gửi yêu cầu đặt chuyến hợp lệ</x:v>
+        <x:v>Xác định vị trí và lọc tài xế sẵn sàng</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str">
-        <x:v>Đã nhập đủ thông tin chuyến</x:v>
+        <x:v>Yêu cầu chuyến đã được tạo</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>Nhấn Đặt xe</x:v>
+        <x:v>Bắt đầu tìm tài xế</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Điểm đón/đến hợp lệ; loại xe 4 chỗ</x:v>
+        <x:v>Driver A: Available; Driver B: Busy</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Hệ thống tạo và lưu yêu cầu đặt chuyến</x:v>
+        <x:v>Hệ thống sử dụng vị trí điểm đón và chỉ đưa tài xế sẵn sàng vào danh sách xét</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="54" customHeight="1">
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>TC-CAB-005</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>Xác định vị trí</x:v>
+        <x:v>Tìm tài xế</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Xác định vị trí điểm đón để tìm tài xế</x:v>
+        <x:v>Chọn tài xế phù hợp và ưu tiên gần điểm đón</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>Yêu cầu đặt chuyến đã được tạo</x:v>
+        <x:v>Có nhiều tài xế sẵn sàng</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Bắt đầu tìm tài xế</x:v>
+        <x:v>Thực hiện chọn tài xế cho chuyến</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Điểm đón hợp lệ</x:v>
+        <x:v>Driver A: 4 chỗ, 0.5 km; Driver B: 4 chỗ, 2 km; Driver C: xe không phù hợp</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Hệ thống sử dụng vị trí điểm đón trong quá trình tìm tài xế</x:v>
+        <x:v>Hệ thống chỉ chọn tài xế phù hợp và ưu tiên Driver A theo quy tắc</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="12" t="str">
         <x:v>TC-CAB-006</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Lọc tài xế sẵn sàng</x:v>
+        <x:v>Gửi yêu cầu cho tài xế</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Chỉ lọc tài xế ở trạng thái sẵn sàng</x:v>
+        <x:v>Gửi yêu cầu chuyến đến tài xế đã chọn</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>Có tài xế sẵn sàng và không sẵn sàng trong khu vực</x:v>
+        <x:v>Đã chọn được tài xế phù hợp</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>Thực hiện tìm tài xế</x:v>
+        <x:v>Gửi yêu cầu chuyến</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Driver A: Available; Driver B: Busy</x:v>
+        <x:v>Tài xế: DRV001</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>Chỉ tài xế sẵn sàng được đưa vào danh sách xét</x:v>
+        <x:v>Tài xế nhận được thông báo với thông tin chuyến cần thiết</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="54" customHeight="1">
+    <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="12" t="str">
         <x:v>TC-CAB-007</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Xác định tài xế phù hợp</x:v>
+        <x:v>Phân công chuyến</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>Xác định tài xế phù hợp với yêu cầu chuyến</x:v>
+        <x:v>Phân công sau khi tài xế chấp nhận</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str">
-        <x:v>Có các tài xế sẵn sàng</x:v>
+        <x:v>Tài xế đang nhận yêu cầu hợp lệ</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>Thực hiện tìm tài xế cho chuyến</x:v>
+        <x:v>Tài xế chọn Chấp nhận; khách hàng mở chi tiết chuyến</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Loại xe yêu cầu: 4 chỗ</x:v>
+        <x:v>Phản hồi: Accept</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>Hệ thống chỉ chọn tài xế đáp ứng yêu cầu chuyến và tiêu chí vận hành</x:v>
+        <x:v>Hệ thống phân công tài xế; khách hàng nhận thông báo và xem được thông tin tài xế, trạng thái chuyến</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="54" customHeight="1">
+    <x:row r="9" ht="60" customHeight="1">
       <x:c r="A9" s="12" t="str">
         <x:v>TC-CAB-008</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>Ưu tiên tài xế gần khách</x:v>
+        <x:v>Tìm lại tài xế</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>Ưu tiên tài xế phù hợp ở gần điểm đón</x:v>
+        <x:v>Tìm tài xế khác sau khi từ chối</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
-        <x:v>Có từ hai tài xế phù hợp ở các khoảng cách khác nhau</x:v>
+        <x:v>Tài xế đầu tiên từ chối; còn tài xế phù hợp</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
-        <x:v>Thực hiện tìm tài xế</x:v>
+        <x:v>Ghi nhận từ chối và tiếp tục tìm</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Driver A: 0.5 km; Driver B: 2 km</x:v>
+        <x:v>Driver A: Reject; Driver B: Available</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>Hệ thống ưu tiên tài xế gần điểm đón theo quy tắc nghiệp vụ</x:v>
+        <x:v>Hệ thống không phân công Driver A và gửi yêu cầu mới cho Driver B</x:v>
       </x:c>
       <x:c r="H9" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
       <x:c r="A10" s="12" t="str">
         <x:v>TC-CAB-009</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Gửi yêu cầu cho tài xế</x:v>
+        <x:v>Tìm lại tài xế</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Gửi yêu cầu chuyến đến tài xế phù hợp</x:v>
+        <x:v>Tìm tài xế khác khi quá thời gian phản hồi</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Đã chọn được tài xế phù hợp</x:v>
+        <x:v>Tài xế không phản hồi; còn tài xế phù hợp</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Gửi yêu cầu chuyến</x:v>
+        <x:v>Chờ hết thời gian quy định và tiếp tục tìm</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
-        <x:v>Yêu cầu chuyến hợp lệ</x:v>
+        <x:v>Driver A: no response; Driver B: Available</x:v>
       </x:c>
       <x:c r="G10" s="12" t="str">
-        <x:v>Tài xế nhận được yêu cầu với thông tin chuyến cần thiết</x:v>
+        <x:v>Hệ thống xác định timeout và gửi yêu cầu cho Driver B</x:v>
       </x:c>
       <x:c r="H10" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="54" customHeight="1">
+    <x:row r="11" ht="60" customHeight="1">
       <x:c r="A11" s="12" t="str">
         <x:v>TC-CAB-010</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Tài xế chấp nhận</x:v>
+        <x:v>Tìm tài xế</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Ghi nhận tài xế chấp nhận chuyến</x:v>
+        <x:v>Thông báo khi không còn tài xế phù hợp</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>Tài xế đang nhận yêu cầu chuyến</x:v>
+        <x:v>Không có tài xế phù hợp</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Tài xế chọn Chấp nhận</x:v>
+        <x:v>Thực hiện tìm tài xế</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Phản hồi: Accept</x:v>
+        <x:v>Không có driver Available phù hợp</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
-        <x:v>Hệ thống ghi nhận chấp nhận và phân công tài xế cho chuyến</x:v>
+        <x:v>Hệ thống không phân công tài xế và thông báo rõ cho khách hàng</x:v>
       </x:c>
       <x:c r="H11" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="54" customHeight="1">
+    <x:row r="12" ht="60" customHeight="1">
       <x:c r="A12" s="12" t="str">
         <x:v>TC-CAB-011</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>Tài xế từ chối</x:v>
+        <x:v>Theo dõi chuyến</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>Xử lý tài xế từ chối chuyến</x:v>
+        <x:v>Xem thông tin tài xế và ETA</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>Tài xế đang nhận yêu cầu chuyến</x:v>
+        <x:v>Chuyến đã được phân công; có vị trí tài xế</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>Tài xế chọn Từ chối</x:v>
+        <x:v>Mở chi tiết chuyến</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
-        <x:v>Phản hồi: Reject</x:v>
+        <x:v>Tài xế: DRV001; vị trí hợp lệ</x:v>
       </x:c>
       <x:c r="G12" s="12" t="str">
-        <x:v>Hệ thống ghi nhận từ chối và không phân công tài xế này</x:v>
+        <x:v>Hiển thị đúng thông tin tài xế và thời gian dự kiến đến</x:v>
       </x:c>
       <x:c r="H12" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
       <x:c r="A13" s="12" t="str">
         <x:v>TC-CAB-012</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>Xử lý không phản hồi</x:v>
+        <x:v>Theo dõi chuyến</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>Xử lý hết thời gian phản hồi của tài xế</x:v>
+        <x:v>Xem trạng thái hiện tại của chuyến</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
-        <x:v>Tài xế đã nhận yêu cầu nhưng chưa phản hồi</x:v>
+        <x:v>Chuyến tồn tại</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
-        <x:v>Chờ hết thời gian quy định</x:v>
+        <x:v>Mở chi tiết chuyến</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
-        <x:v>Thời gian chờ theo quy định</x:v>
+        <x:v>Trạng thái: Driver assigned</x:v>
       </x:c>
       <x:c r="G13" s="12" t="str">
-        <x:v>Hệ thống xác định tài xế không phản hồi và không giữ phân công</x:v>
+        <x:v>Hiển thị đúng trạng thái chuyến hiện tại</x:v>
       </x:c>
       <x:c r="H13" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
       <x:c r="A14" s="12" t="str">
         <x:v>TC-CAB-013</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>Tìm tài xế khác</x:v>
+        <x:v>Thực hiện chuyến</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>Tìm tài xế khác sau khi tài xế đầu tiên từ chối</x:v>
+        <x:v>Cập nhật tuần tự trạng thái chuyến</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>Tài xế đầu tiên đã từ chối</x:v>
+        <x:v>Tài xế đã được phân công</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>Tiếp tục tìm tài xế</x:v>
+        <x:v>Cập nhật Đã đến; Đã đón khách; Đang di chuyển; Hoàn thành</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>Có tài xế phù hợp khác</x:v>
+        <x:v>Chuỗi trạng thái hợp lệ</x:v>
       </x:c>
       <x:c r="G14" s="12" t="str">
-        <x:v>Hệ thống loại tài xế đã từ chối và gửi yêu cầu cho tài xế khác</x:v>
+        <x:v>Hệ thống lưu đúng thứ tự trạng thái và thông báo mỗi thay đổi cho khách hàng</x:v>
       </x:c>
       <x:c r="H14" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="54" customHeight="1">
+    <x:row r="15" ht="60" customHeight="1">
       <x:c r="A15" s="12" t="str">
         <x:v>TC-CAB-014</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>Xem thông tin tài xế</x:v>
+        <x:v>Tính cước</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
-        <x:v>Khách hàng xem thông tin tài xế đã được phân công</x:v>
+        <x:v>Tính và hiển thị cước sau khi hoàn thành</x:v>
       </x:c>
       <x:c r="D15" s="12" t="str">
-        <x:v>Chuyến đã được phân công</x:v>
+        <x:v>Chuyến đã hoàn thành</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
-        <x:v>Mở chi tiết chuyến</x:v>
+        <x:v>Yêu cầu tính cước; mở màn hình thanh toán</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
-        <x:v>Tài xế đã được gán</x:v>
+        <x:v>Khoảng cách hợp lệ; Xe: 4 chỗ</x:v>
       </x:c>
       <x:c r="G15" s="12" t="str">
-        <x:v>Hiển thị thông tin tài xế theo quyền xem của khách hàng</x:v>
+        <x:v>Hệ thống xác định cước và hiển thị đúng số tiền phải trả</x:v>
       </x:c>
       <x:c r="H15" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="54" customHeight="1">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="12" t="str">
         <x:v>TC-CAB-015</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>Xem ETA</x:v>
+        <x:v>Thanh toán tiền mặt</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>Khách hàng xem thời gian dự kiến tài xế đến</x:v>
+        <x:v>Ghi nhận thanh toán tiền mặt</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str">
-        <x:v>Chuyến đã được phân công và có vị trí tài xế</x:v>
+        <x:v>Chuyến hoàn thành và có cước</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
-        <x:v>Mở chi tiết chuyến</x:v>
+        <x:v>Chọn Tiền mặt; xác nhận</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
-        <x:v>Vị trí tài xế hợp lệ</x:v>
+        <x:v>Cước: 75,000 VND</x:v>
       </x:c>
       <x:c r="G16" s="12" t="str">
-        <x:v>Hiển thị thời gian dự kiến đến</x:v>
+        <x:v>Hệ thống ghi nhận giao dịch tiền mặt và gửi thông báo kết quả</x:v>
       </x:c>
       <x:c r="H16" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="54" customHeight="1">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="60" customHeight="1">
       <x:c r="A17" s="12" t="str">
         <x:v>TC-CAB-016</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
-        <x:v>Xem trạng thái chuyến</x:v>
+        <x:v>Thanh toán điện tử</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
-        <x:v>Khách hàng xem trạng thái hiện tại của chuyến</x:v>
+        <x:v>Ghi nhận thanh toán điện tử thành công</x:v>
       </x:c>
       <x:c r="D17" s="12" t="str">
-        <x:v>Chuyến tồn tại</x:v>
+        <x:v>Chuyến hoàn thành; phương thức điện tử hợp lệ</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
-        <x:v>Mở chi tiết chuyến</x:v>
+        <x:v>Gửi giao dịch; nhận kết quả thành công</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
-        <x:v>Trạng thái: Driver assigned</x:v>
+        <x:v>Phương thức: E-wallet; Kết quả: Success</x:v>
       </x:c>
       <x:c r="G17" s="12" t="str">
-        <x:v>Hiển thị đúng trạng thái chuyến hiện tại</x:v>
+        <x:v>Hệ thống ghi nhận giao dịch thành công và thông báo khách hàng</x:v>
       </x:c>
       <x:c r="H17" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="54" customHeight="1">
+    <x:row r="18" ht="60" customHeight="1">
       <x:c r="A18" s="12" t="str">
         <x:v>TC-CAB-017</x:v>
       </x:c>
       <x:c r="B18" s="12" t="str">
-        <x:v>Cập nhật đã đến</x:v>
+        <x:v>Thanh toán điện tử</x:v>
       </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>Tài xế cập nhật trạng thái đã đến điểm đón</x:v>
+        <x:v>Xử lý thanh toán điện tử thất bại</x:v>
       </x:c>
       <x:c r="D18" s="12" t="str">
-        <x:v>Tài xế được phân công cho chuyến</x:v>
+        <x:v>Đã gửi giao dịch đến nhà cung cấp</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
-        <x:v>Chọn Đã đến</x:v>
+        <x:v>Nhận kết quả thất bại</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str">
-        <x:v>Trạng thái mới: Arrived</x:v>
+        <x:v>Kết quả: Failed</x:v>
       </x:c>
       <x:c r="G18" s="12" t="str">
-        <x:v>Hệ thống cập nhật trạng thái chuyến là Đã đến</x:v>
+        <x:v>Hệ thống thông báo thất bại và cho phép xử lý lại theo chính sách</x:v>
       </x:c>
       <x:c r="H18" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="54" customHeight="1">
+    <x:row r="19" ht="60" customHeight="1">
       <x:c r="A19" s="12" t="str">
         <x:v>TC-CAB-018</x:v>
       </x:c>
       <x:c r="B19" s="12" t="str">
-        <x:v>Cập nhật đã đón</x:v>
+        <x:v>Thông báo chuyến</x:v>
       </x:c>
       <x:c r="C19" s="12" t="str">
-        <x:v>Tài xế cập nhật trạng thái đã đón khách</x:v>
+        <x:v>Gửi thông báo cho khách hàng và tài xế khi tạo yêu cầu</x:v>
       </x:c>
       <x:c r="D19" s="12" t="str">
-        <x:v>Chuyến đang ở trạng thái Đã đến</x:v>
+        <x:v>Khách hàng gửi yêu cầu hợp lệ; đã chọn tài xế</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
-        <x:v>Chọn Đã đón khách</x:v>
+        <x:v>Gửi yêu cầu chuyến</x:v>
       </x:c>
       <x:c r="F19" s="12" t="str">
-        <x:v>Trạng thái mới: Picked up</x:v>
+        <x:v>Yêu cầu: TRIP001</x:v>
       </x:c>
       <x:c r="G19" s="12" t="str">
-        <x:v>Hệ thống cập nhật trạng thái chuyến là Đã đón khách</x:v>
+        <x:v>Khách hàng nhận thông báo tiếp nhận; tài xế nhận thông báo chuyến mới</x:v>
       </x:c>
       <x:c r="H19" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="60" customHeight="1">
       <x:c r="A20" s="12" t="str">
         <x:v>TC-CAB-019</x:v>
       </x:c>
       <x:c r="B20" s="12" t="str">
-        <x:v>Cập nhật đang di chuyển</x:v>
+        <x:v>Thông báo chuyến</x:v>
       </x:c>
       <x:c r="C20" s="12" t="str">
-        <x:v>Tài xế cập nhật trạng thái đang di chuyển</x:v>
+        <x:v>Gửi thông báo khi tài xế đến điểm đón</x:v>
       </x:c>
       <x:c r="D20" s="12" t="str">
-        <x:v>Chuyến đã đón khách</x:v>
+        <x:v>Chuyến đang diễn ra</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
-        <x:v>Chọn Đang di chuyển</x:v>
+        <x:v>Tài xế cập nhật Đã đến</x:v>
       </x:c>
       <x:c r="F20" s="12" t="str">
-        <x:v>Trạng thái mới: In progress</x:v>
+        <x:v>Trạng thái: Arrived</x:v>
       </x:c>
       <x:c r="G20" s="12" t="str">
-        <x:v>Hệ thống cập nhật trạng thái chuyến là Đang di chuyển</x:v>
+        <x:v>Khách hàng nhận thông báo trạng thái Đã đến</x:v>
       </x:c>
       <x:c r="H20" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="60" customHeight="1">
       <x:c r="A21" s="12" t="str">
         <x:v>TC-CAB-020</x:v>
       </x:c>
       <x:c r="B21" s="12" t="str">
-        <x:v>Cập nhật hoàn thành</x:v>
+        <x:v>Quản lý khách hàng</x:v>
       </x:c>
       <x:c r="C21" s="12" t="str">
-        <x:v>Tài xế cập nhật trạng thái hoàn thành</x:v>
+        <x:v>Cập nhật thông tin khách hàng</x:v>
       </x:c>
       <x:c r="D21" s="12" t="str">
-        <x:v>Chuyến đang di chuyển</x:v>
+        <x:v>Nhân viên có quyền quản lý khách hàng</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
-        <x:v>Chọn Hoàn thành</x:v>
+        <x:v>Mở hồ sơ khách hàng; cập nhật; lưu</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
-        <x:v>Trạng thái mới: Completed</x:v>
+        <x:v>Khách hàng: CUS001</x:v>
       </x:c>
       <x:c r="G21" s="12" t="str">
-        <x:v>Hệ thống cập nhật trạng thái chuyến là Hoàn thành</x:v>
+        <x:v>Thông tin khách hàng được cập nhật và lưu đúng</x:v>
       </x:c>
       <x:c r="H21" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="60" customHeight="1">
       <x:c r="A22" s="12" t="str">
         <x:v>TC-CAB-021</x:v>
       </x:c>
       <x:c r="B22" s="12" t="str">
-        <x:v>Tính cước</x:v>
+        <x:v>Quản lý tài xế và phương tiện</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>Tính cước cho chuyến hoàn thành</x:v>
+        <x:v>Cập nhật hồ sơ tài xế và phương tiện</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>Chuyến đã hoàn thành</x:v>
+        <x:v>Nhân viên có quyền quản lý</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
-        <x:v>Yêu cầu tính cước</x:v>
+        <x:v>Cập nhật hồ sơ tài xế; cập nhật phương tiện; lưu</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str">
-        <x:v>Khoảng cách và loại xe hợp lệ</x:v>
+        <x:v>Tài xế: DRV001; Xe: CAR001</x:v>
       </x:c>
       <x:c r="G22" s="12" t="str">
-        <x:v>Hệ thống xác định cước theo thông tin chuyến và loại dịch vụ</x:v>
+        <x:v>Thông tin tài xế và phương tiện được cập nhật, lưu đúng</x:v>
       </x:c>
       <x:c r="H22" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="60" customHeight="1">
       <x:c r="A23" s="12" t="str">
         <x:v>TC-CAB-022</x:v>
       </x:c>
       <x:c r="B23" s="12" t="str">
-        <x:v>Hiển thị số tiền</x:v>
+        <x:v>Giám sát chuyến đi</x:v>
       </x:c>
       <x:c r="C23" s="12" t="str">
-        <x:v>Hiển thị số tiền phải thanh toán</x:v>
+        <x:v>Theo dõi chuyến đang diễn ra</x:v>
       </x:c>
       <x:c r="D23" s="12" t="str">
-        <x:v>Cước chuyến đã được tính</x:v>
+        <x:v>Nhân viên có quyền giám sát</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
-        <x:v>Mở màn hình thanh toán</x:v>
+        <x:v>Mở danh sách chuyến đang diễn ra</x:v>
       </x:c>
       <x:c r="F23" s="12" t="str">
-        <x:v>Cước: 75,000 VND</x:v>
+        <x:v>Chuyến: TRIP001</x:v>
       </x:c>
       <x:c r="G23" s="12" t="str">
-        <x:v>Hiển thị đúng số tiền cần thanh toán</x:v>
+        <x:v>Hiển thị thông tin và trạng thái hiện tại của chuyến</x:v>
       </x:c>
       <x:c r="H23" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="60" customHeight="1">
       <x:c r="A24" s="12" t="str">
         <x:v>TC-CAB-023</x:v>
       </x:c>
       <x:c r="B24" s="12" t="str">
-        <x:v>Thanh toán tiền mặt</x:v>
+        <x:v>Xử lý sự cố</x:v>
       </x:c>
       <x:c r="C24" s="12" t="str">
-        <x:v>Ghi nhận thanh toán bằng tiền mặt</x:v>
+        <x:v>Ghi nhận kết quả xử lý sự cố</x:v>
       </x:c>
       <x:c r="D24" s="12" t="str">
-        <x:v>Chuyến hoàn thành và có số tiền phải trả</x:v>
+        <x:v>Nhân viên có quyền xử lý; chuyến có vấn đề</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
-        <x:v>Chọn Tiền mặt và xác nhận</x:v>
+        <x:v>Mở sự cố; nhập kết quả xử lý; lưu</x:v>
       </x:c>
       <x:c r="F24" s="12" t="str">
-        <x:v>Phương thức: Cash</x:v>
+        <x:v>Sự cố: tài xế không đến</x:v>
       </x:c>
       <x:c r="G24" s="12" t="str">
-        <x:v>Hệ thống ghi nhận giao dịch thanh toán tiền mặt</x:v>
+        <x:v>Hệ thống lưu kết quả xử lý cho chuyến</x:v>
       </x:c>
       <x:c r="H24" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="54" customHeight="1">
+    <x:row r="25" ht="60" customHeight="1">
       <x:c r="A25" s="12" t="str">
         <x:v>TC-CAB-024</x:v>
       </x:c>
       <x:c r="B25" s="12" t="str">
-        <x:v>Thanh toán điện tử</x:v>
+        <x:v>Tra cứu giao dịch</x:v>
       </x:c>
       <x:c r="C25" s="12" t="str">
-        <x:v>Gửi giao dịch thanh toán điện tử</x:v>
+        <x:v>Tra cứu giao dịch theo mã</x:v>
       </x:c>
       <x:c r="D25" s="12" t="str">
-        <x:v>Chuyến hoàn thành và có phương thức điện tử hợp lệ</x:v>
+        <x:v>Nhân viên có quyền tra cứu</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
-        <x:v>Chọn thanh toán điện tử và xác nhận</x:v>
+        <x:v>Tìm kiếm giao dịch</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
-        <x:v>Phương thức: E-wallet</x:v>
+        <x:v>Mã giao dịch: TXN001</x:v>
       </x:c>
       <x:c r="G25" s="12" t="str">
-        <x:v>Hệ thống gửi yêu cầu thanh toán đến nhà cung cấp bên ngoài</x:v>
+        <x:v>Hiển thị đúng thông tin giao dịch</x:v>
       </x:c>
       <x:c r="H25" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="54" customHeight="1">
+        <x:v>Medium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="60" customHeight="1">
       <x:c r="A26" s="12" t="str">
         <x:v>TC-CAB-025</x:v>
       </x:c>
       <x:c r="B26" s="12" t="str">
-        <x:v>Xử lý thanh toán thất bại</x:v>
+        <x:v>Phân quyền</x:v>
       </x:c>
       <x:c r="C26" s="12" t="str">
-        <x:v>Xử lý giao dịch điện tử thất bại</x:v>
+        <x:v>Từ chối thao tác quản trị không được cấp quyền</x:v>
       </x:c>
       <x:c r="D26" s="12" t="str">
-        <x:v>Đã gửi giao dịch đến nhà cung cấp</x:v>
+        <x:v>Người dùng có quyền hạn chế</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
-        <x:v>Nhận kết quả thất bại</x:v>
+        <x:v>Truy cập chức năng quản trị không được cấp</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
-        <x:v>Kết quả: Failed</x:v>
+        <x:v>Vai trò: Operator limited</x:v>
       </x:c>
       <x:c r="G26" s="12" t="str">
-        <x:v>Hệ thống thông báo thất bại và cho phép xử lý lại theo chính sách</x:v>
+        <x:v>Hệ thống từ chối thao tác và không thay đổi dữ liệu</x:v>
       </x:c>
       <x:c r="H26" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="54" customHeight="1">
+    <x:row r="27" ht="60" customHeight="1">
       <x:c r="A27" s="12" t="str">
         <x:v>TC-CAB-026</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>Thông báo đặt xe</x:v>
+        <x:v>Đánh giá tài xế</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>Gửi thông báo khi yêu cầu đặt xe được tiếp nhận</x:v>
+        <x:v>Đánh giá tài xế sau khi chuyến hoàn thành</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str">
-        <x:v>Khách hàng gửi yêu cầu hợp lệ</x:v>
+        <x:v>Khách hàng là người đi chuyến hoàn thành</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
-        <x:v>Gửi yêu cầu đặt xe</x:v>
+        <x:v>Mở đánh giá; chọn điểm; gửi</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
-        <x:v>Yêu cầu chuyến hợp lệ</x:v>
+        <x:v>Điểm: 5; nhận xét: Tốt</x:v>
       </x:c>
       <x:c r="G27" s="12" t="str">
-        <x:v>Khách hàng nhận được thông báo yêu cầu đã được tiếp nhận</x:v>
+        <x:v>Hệ thống lưu đánh giá cho đúng tài xế và chuyến</x:v>
       </x:c>
       <x:c r="H27" s="13" t="str">
         <x:v>Medium</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="54" customHeight="1">
+    <x:row r="28" ht="60" customHeight="1">
       <x:c r="A28" s="12" t="str">
         <x:v>TC-CAB-027</x:v>
       </x:c>
       <x:c r="B28" s="12" t="str">
-        <x:v>Thông báo cho tài xế</x:v>
+        <x:v>Đánh giá tài xế</x:v>
       </x:c>
       <x:c r="C28" s="12" t="str">
-        <x:v>Gửi thông báo yêu cầu chuyến cho tài xế</x:v>
+        <x:v>Không cho đánh giá trước khi chuyến hoàn thành</x:v>
       </x:c>
       <x:c r="D28" s="12" t="str">
-        <x:v>Đã chọn tài xế phù hợp</x:v>
+        <x:v>Khách hàng có chuyến chưa hoàn thành</x:v>
       </x:c>
       <x:c r="E28" s="12" t="str">
-        <x:v>Gửi yêu cầu chuyến</x:v>
+        <x:v>Mở đánh giá cho chuyến đang di chuyển</x:v>
       </x:c>
       <x:c r="F28" s="12" t="str">
-        <x:v>Tài xế sẵn sàng</x:v>
+        <x:v>Trạng thái: In progress</x:v>
       </x:c>
       <x:c r="G28" s="12" t="str">
-        <x:v>Tài xế nhận được thông báo chuyến mới</x:v>
+        <x:v>Hệ thống không cho gửi đánh giá</x:v>
       </x:c>
       <x:c r="H28" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="54" customHeight="1">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="60" customHeight="1">
       <x:c r="A29" s="12" t="str">
         <x:v>TC-CAB-028</x:v>
       </x:c>
       <x:c r="B29" s="12" t="str">
-        <x:v>Thông báo trạng thái chuyến</x:v>
+        <x:v>Lịch sử chuyến</x:v>
       </x:c>
       <x:c r="C29" s="12" t="str">
-        <x:v>Gửi thông báo khi trạng thái chuyến thay đổi</x:v>
+        <x:v>Xem lịch sử chuyến và số tiền phải trả</x:v>
       </x:c>
       <x:c r="D29" s="12" t="str">
-        <x:v>Chuyến đang diễn ra</x:v>
+        <x:v>Khách hàng đã có chuyến</x:v>
       </x:c>
       <x:c r="E29" s="12" t="str">
-        <x:v>Tài xế cập nhật một trạng thái chuyến</x:v>
+        <x:v>Mở Lịch sử chuyến</x:v>
       </x:c>
       <x:c r="F29" s="12" t="str">
-        <x:v>Trạng thái: Arrived</x:v>
+        <x:v>Khách hàng: CUS001</x:v>
       </x:c>
       <x:c r="G29" s="12" t="str">
-        <x:v>Khách hàng nhận được thông báo trạng thái mới</x:v>
+        <x:v>Hiển thị các chuyến của khách hàng cùng số tiền</x:v>
       </x:c>
       <x:c r="H29" s="13" t="str">
         <x:v>Medium</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="54" customHeight="1">
+    <x:row r="30" ht="60" customHeight="1">
       <x:c r="A30" s="12" t="str">
         <x:v>TC-CAB-029</x:v>
       </x:c>
       <x:c r="B30" s="12" t="str">
-        <x:v>Thông báo thanh toán</x:v>
+        <x:v>Báo cáo hoạt động</x:v>
       </x:c>
       <x:c r="C30" s="12" t="str">
-        <x:v>Gửi thông báo kết quả thanh toán</x:v>
+        <x:v>Xem báo cáo hoạt động theo kỳ</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>Có kết quả thanh toán</x:v>
+        <x:v>Quản lý có quyền xem báo cáo</x:v>
       </x:c>
       <x:c r="E30" s="12" t="str">
-        <x:v>Hoàn tất thanh toán</x:v>
+        <x:v>Chọn kỳ báo cáo; mở báo cáo</x:v>
       </x:c>
       <x:c r="F30" s="12" t="str">
-        <x:v>Kết quả: Success</x:v>
+        <x:v>Kỳ: Tháng 09/2026</x:v>
       </x:c>
       <x:c r="G30" s="12" t="str">
-        <x:v>Khách hàng nhận được thông báo kết quả thanh toán</x:v>
+        <x:v>Hiển thị số chuyến, doanh thu, tỷ lệ hoàn thành, tỷ lệ hủy và hiệu quả tài xế</x:v>
       </x:c>
       <x:c r="H30" s="13" t="str">
         <x:v>Medium</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="54" customHeight="1">
+    <x:row r="31" ht="60" customHeight="1">
       <x:c r="A31" s="12" t="str">
         <x:v>TC-CAB-030</x:v>
       </x:c>
       <x:c r="B31" s="12" t="str">
-        <x:v>Quản lý khách hàng</x:v>
+        <x:v>Phân quyền quản trị</x:v>
       </x:c>
       <x:c r="C31" s="12" t="str">
-        <x:v>Nhân viên vận hành cập nhật thông tin khách hàng</x:v>
+        <x:v>Không cho người dùng hạn chế sửa dữ liệu vận hành</x:v>
       </x:c>
       <x:c r="D31" s="12" t="str">
-        <x:v>Nhân viên có quyền quản lý khách hàng</x:v>
+        <x:v>Người dùng có quyền hạn chế</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
-        <x:v>Mở hồ sơ khách hàng và lưu thay đổi</x:v>
+        <x:v>Thử sửa khách hàng, tài xế và phương tiện</x:v>
       </x:c>
       <x:c r="F31" s="12" t="str">
-        <x:v>Khách hàng: CUS001</x:v>
+        <x:v>Vai trò: Operator limited</x:v>
       </x:c>
       <x:c r="G31" s="12" t="str">
-        <x:v>Thông tin khách hàng được cập nhật và lưu đúng</x:v>
+        <x:v>Mọi thao tác ngoài quyền bị từ chối và dữ liệu không thay đổi</x:v>
       </x:c>
       <x:c r="H31" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="54" customHeight="1">
-      <x:c r="A32" s="12" t="str">
-        <x:v>TC-CAB-031</x:v>
-      </x:c>
-      <x:c r="B32" s="12" t="str">
-        <x:v>Quản lý tài xế</x:v>
-      </x:c>
-      <x:c r="C32" s="12" t="str">
-        <x:v>Nhân viên vận hành cập nhật hồ sơ tài xế</x:v>
-      </x:c>
-      <x:c r="D32" s="12" t="str">
-        <x:v>Nhân viên có quyền quản lý tài xế</x:v>
-      </x:c>
-      <x:c r="E32" s="12" t="str">
-        <x:v>Mở hồ sơ tài xế và lưu thay đổi</x:v>
-      </x:c>
-      <x:c r="F32" s="12" t="str">
-        <x:v>Tài xế: DRV001</x:v>
-      </x:c>
-      <x:c r="G32" s="12" t="str">
-        <x:v>Thông tin tài xế được cập nhật và lưu đúng</x:v>
-      </x:c>
-      <x:c r="H32" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="54" customHeight="1">
-      <x:c r="A33" s="12" t="str">
-        <x:v>TC-CAB-032</x:v>
-      </x:c>
-      <x:c r="B33" s="12" t="str">
-        <x:v>Quản lý phương tiện</x:v>
-      </x:c>
-      <x:c r="C33" s="12" t="str">
-        <x:v>Nhân viên vận hành cập nhật thông tin phương tiện</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="str">
-        <x:v>Nhân viên có quyền quản lý phương tiện</x:v>
-      </x:c>
-      <x:c r="E33" s="12" t="str">
-        <x:v>Mở phương tiện và lưu thay đổi</x:v>
-      </x:c>
-      <x:c r="F33" s="12" t="str">
-        <x:v>Xe: CAR001</x:v>
-      </x:c>
-      <x:c r="G33" s="12" t="str">
-        <x:v>Thông tin phương tiện được cập nhật và lưu đúng</x:v>
-      </x:c>
-      <x:c r="H33" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="54" customHeight="1">
-      <x:c r="A34" s="12" t="str">
-        <x:v>TC-CAB-033</x:v>
-      </x:c>
-      <x:c r="B34" s="12" t="str">
-        <x:v>Giám sát chuyến đi</x:v>
-      </x:c>
-      <x:c r="C34" s="12" t="str">
-        <x:v>Nhân viên vận hành theo dõi chuyến đang diễn ra</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="str">
-        <x:v>Nhân viên có quyền giám sát</x:v>
-      </x:c>
-      <x:c r="E34" s="12" t="str">
-        <x:v>Mở danh sách chuyến đang diễn ra</x:v>
-      </x:c>
-      <x:c r="F34" s="12" t="str">
-        <x:v>Chuyến: TRIP001</x:v>
-      </x:c>
-      <x:c r="G34" s="12" t="str">
-        <x:v>Hiển thị thông tin và trạng thái hiện tại của chuyến</x:v>
-      </x:c>
-      <x:c r="H34" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="54" customHeight="1">
-      <x:c r="A35" s="12" t="str">
-        <x:v>TC-CAB-034</x:v>
-      </x:c>
-      <x:c r="B35" s="12" t="str">
-        <x:v>Xử lý sự cố</x:v>
-      </x:c>
-      <x:c r="C35" s="12" t="str">
-        <x:v>Nhân viên vận hành ghi nhận xử lý sự cố chuyến</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="str">
-        <x:v>Nhân viên có quyền xử lý sự cố; chuyến có vấn đề</x:v>
-      </x:c>
-      <x:c r="E35" s="12" t="str">
-        <x:v>Mở sự cố, nhập kết quả xử lý và lưu</x:v>
-      </x:c>
-      <x:c r="F35" s="12" t="str">
-        <x:v>Sự cố: tài xế không đến</x:v>
-      </x:c>
-      <x:c r="G35" s="12" t="str">
-        <x:v>Hệ thống lưu kết quả xử lý cho chuyến</x:v>
-      </x:c>
-      <x:c r="H35" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="54" customHeight="1">
-      <x:c r="A36" s="12" t="str">
-        <x:v>TC-CAB-035</x:v>
-      </x:c>
-      <x:c r="B36" s="12" t="str">
-        <x:v>Tra cứu giao dịch</x:v>
-      </x:c>
-      <x:c r="C36" s="12" t="str">
-        <x:v>Nhân viên vận hành tra cứu giao dịch thanh toán</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="str">
-        <x:v>Nhân viên có quyền tra cứu</x:v>
-      </x:c>
-      <x:c r="E36" s="12" t="str">
-        <x:v>Tìm kiếm giao dịch theo mã</x:v>
-      </x:c>
-      <x:c r="F36" s="12" t="str">
-        <x:v>Mã giao dịch: TXN001</x:v>
-      </x:c>
-      <x:c r="G36" s="12" t="str">
-        <x:v>Hệ thống hiển thị đúng thông tin giao dịch</x:v>
-      </x:c>
-      <x:c r="H36" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="54" customHeight="1">
-      <x:c r="A37" s="12" t="str">
-        <x:v>TC-CAB-036</x:v>
-      </x:c>
-      <x:c r="B37" s="12" t="str">
-        <x:v>Phân quyền</x:v>
-      </x:c>
-      <x:c r="C37" s="12" t="str">
-        <x:v>Chỉ cho phép thao tác quản trị theo quyền được cấp</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="str">
-        <x:v>Có người dùng với quyền hạn chế</x:v>
-      </x:c>
-      <x:c r="E37" s="12" t="str">
-        <x:v>Truy cập chức năng quản trị không được cấp</x:v>
-      </x:c>
-      <x:c r="F37" s="12" t="str">
-        <x:v>Vai trò: Operator limited</x:v>
-      </x:c>
-      <x:c r="G37" s="12" t="str">
-        <x:v>Hệ thống từ chối truy cập thao tác không được cấp quyền</x:v>
-      </x:c>
-      <x:c r="H37" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="54" customHeight="1">
-      <x:c r="A38" s="12" t="str">
-        <x:v>TC-CAB-037</x:v>
-      </x:c>
-      <x:c r="B38" s="12" t="str">
-        <x:v>Đánh giá tài xế</x:v>
-      </x:c>
-      <x:c r="C38" s="12" t="str">
-        <x:v>Khách hàng đánh giá tài xế sau chuyến hoàn thành</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="str">
-        <x:v>Khách hàng là người đi chuyến đã hoàn thành</x:v>
-      </x:c>
-      <x:c r="E38" s="12" t="str">
-        <x:v>Mở đánh giá, chọn điểm và gửi</x:v>
-      </x:c>
-      <x:c r="F38" s="12" t="str">
-        <x:v>Điểm: 5; nhận xét: Tốt</x:v>
-      </x:c>
-      <x:c r="G38" s="12" t="str">
-        <x:v>Hệ thống lưu đánh giá cho đúng tài xế và chuyến</x:v>
-      </x:c>
-      <x:c r="H38" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="54" customHeight="1">
-      <x:c r="A39" s="12" t="str">
-        <x:v>TC-CAB-038</x:v>
-      </x:c>
-      <x:c r="B39" s="12" t="str">
-        <x:v>Lịch sử chuyến</x:v>
-      </x:c>
-      <x:c r="C39" s="12" t="str">
-        <x:v>Khách hàng xem lịch sử các chuyến đi</x:v>
-      </x:c>
-      <x:c r="D39" s="12" t="str">
-        <x:v>Khách hàng đã có chuyến trước đó</x:v>
-      </x:c>
-      <x:c r="E39" s="12" t="str">
-        <x:v>Mở Lịch sử chuyến</x:v>
-      </x:c>
-      <x:c r="F39" s="12" t="str">
-        <x:v>Khách hàng: CUS001</x:v>
-      </x:c>
-      <x:c r="G39" s="12" t="str">
-        <x:v>Hiển thị các chuyến của khách hàng cùng số tiền phải trả</x:v>
-      </x:c>
-      <x:c r="H39" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="54" customHeight="1">
-      <x:c r="A40" s="12" t="str">
-        <x:v>TC-CAB-039</x:v>
-      </x:c>
-      <x:c r="B40" s="12" t="str">
-        <x:v>Báo cáo hoạt động</x:v>
-      </x:c>
-      <x:c r="C40" s="12" t="str">
-        <x:v>Quản lý xem báo cáo hoạt động</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="str">
-        <x:v>Quản lý có quyền xem báo cáo</x:v>
-      </x:c>
-      <x:c r="E40" s="12" t="str">
-        <x:v>Chọn kỳ báo cáo và mở báo cáo</x:v>
-      </x:c>
-      <x:c r="F40" s="12" t="str">
-        <x:v>Kỳ: Tháng 09/2026</x:v>
-      </x:c>
-      <x:c r="G40" s="12" t="str">
-        <x:v>Hiển thị các chỉ số số chuyến, doanh thu, hoàn thành, hủy và hiệu quả tài xế</x:v>
-      </x:c>
-      <x:c r="H40" s="13" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="54" customHeight="1">
-      <x:c r="A41" s="12" t="str">
-        <x:v>TC-CAB-040</x:v>
-      </x:c>
-      <x:c r="B41" s="12" t="str">
-        <x:v>Thông tin đặt chuyến</x:v>
-      </x:c>
-      <x:c r="C41" s="12" t="str">
-        <x:v>Không cho gửi yêu cầu khi thiếu hoặc không hợp lệ</x:v>
-      </x:c>
-      <x:c r="D41" s="12" t="str">
-        <x:v>Màn hình đặt chuyến đang mở</x:v>
-      </x:c>
-      <x:c r="E41" s="12" t="str">
-        <x:v>Để trống hoặc nhập không hợp lệ một trường bắt buộc; nhấn Đặt xe</x:v>
-      </x:c>
-      <x:c r="F41" s="12" t="str">
-        <x:v>Điểm đón: trống</x:v>
-      </x:c>
-      <x:c r="G41" s="12" t="str">
-        <x:v>Hệ thống hiển thị lỗi tương ứng và không tạo yêu cầu chuyến</x:v>
-      </x:c>
-      <x:c r="H41" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="54" customHeight="1">
-      <x:c r="A42" s="12" t="str">
-        <x:v>TC-CAB-041</x:v>
-      </x:c>
-      <x:c r="B42" s="12" t="str">
-        <x:v>Tìm tài xế</x:v>
-      </x:c>
-      <x:c r="C42" s="12" t="str">
-        <x:v>Không chọn tài xế bận hoặc không phù hợp</x:v>
-      </x:c>
-      <x:c r="D42" s="12" t="str">
-        <x:v>Có tài xế Busy và tài xế sai loại xe</x:v>
-      </x:c>
-      <x:c r="E42" s="12" t="str">
-        <x:v>Thực hiện tìm tài xế</x:v>
-      </x:c>
-      <x:c r="F42" s="12" t="str">
-        <x:v>Driver A: Busy; Driver B: xe không phù hợp</x:v>
-      </x:c>
-      <x:c r="G42" s="12" t="str">
-        <x:v>Hệ thống không gửi yêu cầu cho các tài xế không đáp ứng điều kiện</x:v>
-      </x:c>
-      <x:c r="H42" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="54" customHeight="1">
-      <x:c r="A43" s="12" t="str">
-        <x:v>TC-CAB-042</x:v>
-      </x:c>
-      <x:c r="B43" s="12" t="str">
-        <x:v>Phân công chuyến</x:v>
-      </x:c>
-      <x:c r="C43" s="12" t="str">
-        <x:v>Thông báo khách hàng sau khi tài xế chấp nhận</x:v>
-      </x:c>
-      <x:c r="D43" s="12" t="str">
-        <x:v>Tài xế đã nhận yêu cầu hợp lệ</x:v>
-      </x:c>
-      <x:c r="E43" s="12" t="str">
-        <x:v>Tài xế chấp nhận chuyến; khách hàng mở chi tiết chuyến</x:v>
-      </x:c>
-      <x:c r="F43" s="12" t="str">
-        <x:v>Tài xế: DRV001</x:v>
-      </x:c>
-      <x:c r="G43" s="12" t="str">
-        <x:v>Chuyến được phân công; khách hàng thấy thông tin tài xế và trạng thái phù hợp</x:v>
-      </x:c>
-      <x:c r="H43" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="54" customHeight="1">
-      <x:c r="A44" s="12" t="str">
-        <x:v>TC-CAB-043</x:v>
-      </x:c>
-      <x:c r="B44" s="12" t="str">
-        <x:v>Tìm lại tài xế</x:v>
-      </x:c>
-      <x:c r="C44" s="12" t="str">
-        <x:v>Gửi yêu cầu cho tài xế khác sau khi bị từ chối</x:v>
-      </x:c>
-      <x:c r="D44" s="12" t="str">
-        <x:v>Tài xế thứ nhất từ chối; còn tài xế phù hợp</x:v>
-      </x:c>
-      <x:c r="E44" s="12" t="str">
-        <x:v>Ghi nhận từ chối và tiếp tục tìm</x:v>
-      </x:c>
-      <x:c r="F44" s="12" t="str">
-        <x:v>Driver A: Reject; Driver B: Available</x:v>
-      </x:c>
-      <x:c r="G44" s="12" t="str">
-        <x:v>Yêu cầu mới chỉ gửi đến tài xế khác phù hợp</x:v>
-      </x:c>
-      <x:c r="H44" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="54" customHeight="1">
-      <x:c r="A45" s="12" t="str">
-        <x:v>TC-CAB-044</x:v>
-      </x:c>
-      <x:c r="B45" s="12" t="str">
-        <x:v>Tìm lại tài xế</x:v>
-      </x:c>
-      <x:c r="C45" s="12" t="str">
-        <x:v>Tìm tài xế khác khi hết thời gian phản hồi</x:v>
-      </x:c>
-      <x:c r="D45" s="12" t="str">
-        <x:v>Tài xế thứ nhất không phản hồi; còn tài xế phù hợp</x:v>
-      </x:c>
-      <x:c r="E45" s="12" t="str">
-        <x:v>Chờ timeout và tiếp tục tìm</x:v>
-      </x:c>
-      <x:c r="F45" s="12" t="str">
-        <x:v>Driver A: no response; Driver B: Available</x:v>
-      </x:c>
-      <x:c r="G45" s="12" t="str">
-        <x:v>Hệ thống tìm và gửi yêu cầu cho tài xế khác</x:v>
-      </x:c>
-      <x:c r="H45" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="54" customHeight="1">
-      <x:c r="A46" s="12" t="str">
-        <x:v>TC-CAB-045</x:v>
-      </x:c>
-      <x:c r="B46" s="12" t="str">
-        <x:v>Tìm tài xế</x:v>
-      </x:c>
-      <x:c r="C46" s="12" t="str">
-        <x:v>Thông báo khi không còn tài xế phù hợp</x:v>
-      </x:c>
-      <x:c r="D46" s="12" t="str">
-        <x:v>Không có tài xế phù hợp</x:v>
-      </x:c>
-      <x:c r="E46" s="12" t="str">
-        <x:v>Thực hiện tìm tài xế</x:v>
-      </x:c>
-      <x:c r="F46" s="12" t="str">
-        <x:v>Không có driver Available phù hợp</x:v>
-      </x:c>
-      <x:c r="G46" s="12" t="str">
-        <x:v>Hệ thống không phân công và thông báo rõ cho khách hàng</x:v>
-      </x:c>
-      <x:c r="H46" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="54" customHeight="1">
-      <x:c r="A47" s="12" t="str">
-        <x:v>TC-CAB-046</x:v>
-      </x:c>
-      <x:c r="B47" s="12" t="str">
-        <x:v>Thực hiện chuyến</x:v>
-      </x:c>
-      <x:c r="C47" s="12" t="str">
-        <x:v>Cập nhật tuần tự toàn bộ trạng thái chuyến</x:v>
-      </x:c>
-      <x:c r="D47" s="12" t="str">
-        <x:v>Tài xế đã nhận chuyến</x:v>
-      </x:c>
-      <x:c r="E47" s="12" t="str">
-        <x:v>Cập nhật Đã đến; Đã đón khách; Đang di chuyển; Hoàn thành</x:v>
-      </x:c>
-      <x:c r="F47" s="12" t="str">
-        <x:v>Chuỗi trạng thái hợp lệ</x:v>
-      </x:c>
-      <x:c r="G47" s="12" t="str">
-        <x:v>Hệ thống lưu đúng thứ tự trạng thái và gửi thông báo trạng thái</x:v>
-      </x:c>
-      <x:c r="H47" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="54" customHeight="1">
-      <x:c r="A48" s="12" t="str">
-        <x:v>TC-CAB-047</x:v>
-      </x:c>
-      <x:c r="B48" s="12" t="str">
-        <x:v>Thanh toán tiền mặt</x:v>
-      </x:c>
-      <x:c r="C48" s="12" t="str">
-        <x:v>Hoàn tất tính cước và thanh toán tiền mặt</x:v>
-      </x:c>
-      <x:c r="D48" s="12" t="str">
-        <x:v>Chuyến đã hoàn thành</x:v>
-      </x:c>
-      <x:c r="E48" s="12" t="str">
-        <x:v>Tính cước; mở thanh toán; chọn Tiền mặt; xác nhận</x:v>
-      </x:c>
-      <x:c r="F48" s="12" t="str">
-        <x:v>Cước: 75,000 VND</x:v>
-      </x:c>
-      <x:c r="G48" s="12" t="str">
-        <x:v>Hiển thị đúng cước, ghi nhận tiền mặt và gửi thông báo thanh toán</x:v>
-      </x:c>
-      <x:c r="H48" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="54" customHeight="1">
-      <x:c r="A49" s="12" t="str">
-        <x:v>TC-CAB-048</x:v>
-      </x:c>
-      <x:c r="B49" s="12" t="str">
-        <x:v>Thanh toán điện tử</x:v>
-      </x:c>
-      <x:c r="C49" s="12" t="str">
-        <x:v>Ghi nhận thanh toán điện tử thành công</x:v>
-      </x:c>
-      <x:c r="D49" s="12" t="str">
-        <x:v>Nhà cung cấp thanh toán trả kết quả thành công</x:v>
-      </x:c>
-      <x:c r="E49" s="12" t="str">
-        <x:v>Gửi giao dịch và nhận kết quả</x:v>
-      </x:c>
-      <x:c r="F49" s="12" t="str">
-        <x:v>Kết quả: Success</x:v>
-      </x:c>
-      <x:c r="G49" s="12" t="str">
-        <x:v>Hệ thống ghi nhận giao dịch thành công và thông báo khách hàng</x:v>
-      </x:c>
-      <x:c r="H49" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="54" customHeight="1">
-      <x:c r="A50" s="12" t="str">
-        <x:v>TC-CAB-049</x:v>
-      </x:c>
-      <x:c r="B50" s="12" t="str">
-        <x:v>Quản trị vận hành</x:v>
-      </x:c>
-      <x:c r="C50" s="12" t="str">
-        <x:v>Người không đủ quyền không thể quản lý dữ liệu vận hành</x:v>
-      </x:c>
-      <x:c r="D50" s="12" t="str">
-        <x:v>Người dùng có quyền hạn chế</x:v>
-      </x:c>
-      <x:c r="E50" s="12" t="str">
-        <x:v>Thử cập nhật khách hàng, tài xế và phương tiện</x:v>
-      </x:c>
-      <x:c r="F50" s="12" t="str">
-        <x:v>Vai trò: Operator limited</x:v>
-      </x:c>
-      <x:c r="G50" s="12" t="str">
-        <x:v>Mọi thao tác ngoài quyền bị từ chối và không thay đổi dữ liệu</x:v>
-      </x:c>
-      <x:c r="H50" s="13" t="str">
-        <x:v>High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="54" customHeight="1">
-      <x:c r="A51" s="12" t="str">
-        <x:v>TC-CAB-050</x:v>
-      </x:c>
-      <x:c r="B51" s="12" t="str">
-        <x:v>Sau chuyến đi</x:v>
-      </x:c>
-      <x:c r="C51" s="12" t="str">
-        <x:v>Chỉ đánh giá tài xế sau khi chuyến hoàn thành</x:v>
-      </x:c>
-      <x:c r="D51" s="12" t="str">
-        <x:v>Có một chuyến chưa hoàn thành và một chuyến hoàn thành</x:v>
-      </x:c>
-      <x:c r="E51" s="12" t="str">
-        <x:v>Thử đánh giá cả hai chuyến; mở lịch sử chuyến</x:v>
-      </x:c>
-      <x:c r="F51" s="12" t="str">
-        <x:v>Trip A: In progress; Trip B: Completed</x:v>
-      </x:c>
-      <x:c r="G51" s="12" t="str">
-        <x:v>Chỉ Trip B được đánh giá; lịch sử hiển thị thông tin chuyến và số tiền</x:v>
-      </x:c>
-      <x:c r="H51" s="13" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb965b2ad4238471b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R676fb3340c054f44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1839,7 +1318,7 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="56" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
   </x:cols>
@@ -1869,7 +1348,7 @@
         <x:v>Nhập điểm đón</x:v>
       </x:c>
       <x:c r="C2" s="12" t="str">
-        <x:v>TC-CAB-001, TC-CAB-040</x:v>
+        <x:v>TC-CAB-001, TC-CAB-002</x:v>
       </x:c>
       <x:c r="D2" s="13" t="n">
         <x:v>2</x:v>
@@ -1886,7 +1365,7 @@
         <x:v>Nhập điểm đến</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
-        <x:v>TC-CAB-002, TC-CAB-040</x:v>
+        <x:v>TC-CAB-001, TC-CAB-002</x:v>
       </x:c>
       <x:c r="D3" s="13" t="n">
         <x:v>2</x:v>
@@ -1903,7 +1382,7 @@
         <x:v>Chọn loại xe</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
-        <x:v>TC-CAB-003, TC-CAB-040</x:v>
+        <x:v>TC-CAB-001, TC-CAB-002</x:v>
       </x:c>
       <x:c r="D4" s="13" t="n">
         <x:v>2</x:v>
@@ -1920,7 +1399,7 @@
         <x:v>Gửi yêu cầu đặt chuyến</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
-        <x:v>TC-CAB-004, TC-CAB-040</x:v>
+        <x:v>TC-CAB-002, TC-CAB-003</x:v>
       </x:c>
       <x:c r="D5" s="13" t="n">
         <x:v>2</x:v>
@@ -1937,7 +1416,7 @@
         <x:v>Xác định vị trí</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>TC-CAB-005</x:v>
+        <x:v>TC-CAB-004</x:v>
       </x:c>
       <x:c r="D6" s="13" t="n">
         <x:v>1</x:v>
@@ -1954,10 +1433,10 @@
         <x:v>Lọc tài xế sẵn sàng</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>TC-CAB-006, TC-CAB-041, TC-CAB-045</x:v>
+        <x:v>TC-CAB-004, TC-CAB-010</x:v>
       </x:c>
       <x:c r="D7" s="13" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
         <x:v>Covered</x:v>
@@ -1971,10 +1450,10 @@
         <x:v>Xác định tài xế phù hợp</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>TC-CAB-007, TC-CAB-041, TC-CAB-045</x:v>
+        <x:v>TC-CAB-005, TC-CAB-010</x:v>
       </x:c>
       <x:c r="D8" s="13" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
         <x:v>Covered</x:v>
@@ -1988,7 +1467,7 @@
         <x:v>Ưu tiên tài xế gần khách</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>TC-CAB-008</x:v>
+        <x:v>TC-CAB-005</x:v>
       </x:c>
       <x:c r="D9" s="13" t="n">
         <x:v>1</x:v>
@@ -2005,10 +1484,10 @@
         <x:v>Gửi yêu cầu cho tài xế</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>TC-CAB-009</x:v>
+        <x:v>TC-CAB-006, TC-CAB-008, TC-CAB-009</x:v>
       </x:c>
       <x:c r="D10" s="13" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2022,10 +1501,10 @@
         <x:v>Tài xế chấp nhận</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>TC-CAB-010, TC-CAB-042</x:v>
+        <x:v>TC-CAB-007</x:v>
       </x:c>
       <x:c r="D11" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2039,10 +1518,10 @@
         <x:v>Tài xế từ chối</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>TC-CAB-011, TC-CAB-043</x:v>
+        <x:v>TC-CAB-008</x:v>
       </x:c>
       <x:c r="D12" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2056,10 +1535,10 @@
         <x:v>Xử lý không phản hồi</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>TC-CAB-012, TC-CAB-044</x:v>
+        <x:v>TC-CAB-009</x:v>
       </x:c>
       <x:c r="D13" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2073,10 +1552,10 @@
         <x:v>Tìm tài xế khác</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>TC-CAB-013, TC-CAB-043, TC-CAB-044, TC-CAB-045</x:v>
+        <x:v>TC-CAB-008, TC-CAB-009, TC-CAB-010</x:v>
       </x:c>
       <x:c r="D14" s="13" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2090,7 +1569,7 @@
         <x:v>Xem thông tin tài xế</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
-        <x:v>TC-CAB-014, TC-CAB-042</x:v>
+        <x:v>TC-CAB-007, TC-CAB-011</x:v>
       </x:c>
       <x:c r="D15" s="13" t="n">
         <x:v>2</x:v>
@@ -2107,7 +1586,7 @@
         <x:v>Xem ETA</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>TC-CAB-015</x:v>
+        <x:v>TC-CAB-011</x:v>
       </x:c>
       <x:c r="D16" s="13" t="n">
         <x:v>1</x:v>
@@ -2124,7 +1603,7 @@
         <x:v>Xem trạng thái chuyến</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
-        <x:v>TC-CAB-016, TC-CAB-042</x:v>
+        <x:v>TC-CAB-007, TC-CAB-012</x:v>
       </x:c>
       <x:c r="D17" s="13" t="n">
         <x:v>2</x:v>
@@ -2141,10 +1620,10 @@
         <x:v>Cập nhật đã đến</x:v>
       </x:c>
       <x:c r="C18" s="12" t="str">
-        <x:v>TC-CAB-017, TC-CAB-046</x:v>
+        <x:v>TC-CAB-013</x:v>
       </x:c>
       <x:c r="D18" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2158,10 +1637,10 @@
         <x:v>Cập nhật đã đón</x:v>
       </x:c>
       <x:c r="C19" s="12" t="str">
-        <x:v>TC-CAB-018, TC-CAB-046</x:v>
+        <x:v>TC-CAB-013</x:v>
       </x:c>
       <x:c r="D19" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2175,10 +1654,10 @@
         <x:v>Cập nhật đang di chuyển</x:v>
       </x:c>
       <x:c r="C20" s="12" t="str">
-        <x:v>TC-CAB-019, TC-CAB-046</x:v>
+        <x:v>TC-CAB-013</x:v>
       </x:c>
       <x:c r="D20" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2192,7 +1671,7 @@
         <x:v>Cập nhật hoàn thành</x:v>
       </x:c>
       <x:c r="C21" s="12" t="str">
-        <x:v>TC-CAB-020, TC-CAB-046, TC-CAB-050</x:v>
+        <x:v>TC-CAB-013, TC-CAB-026, TC-CAB-027</x:v>
       </x:c>
       <x:c r="D21" s="13" t="n">
         <x:v>3</x:v>
@@ -2209,10 +1688,10 @@
         <x:v>Tính cước</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>TC-CAB-021, TC-CAB-047</x:v>
+        <x:v>TC-CAB-014</x:v>
       </x:c>
       <x:c r="D22" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2226,10 +1705,10 @@
         <x:v>Hiển thị số tiền</x:v>
       </x:c>
       <x:c r="C23" s="12" t="str">
-        <x:v>TC-CAB-022, TC-CAB-047</x:v>
+        <x:v>TC-CAB-014</x:v>
       </x:c>
       <x:c r="D23" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2243,10 +1722,10 @@
         <x:v>Thanh toán tiền mặt</x:v>
       </x:c>
       <x:c r="C24" s="12" t="str">
-        <x:v>TC-CAB-023, TC-CAB-047</x:v>
+        <x:v>TC-CAB-015</x:v>
       </x:c>
       <x:c r="D24" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2260,10 +1739,10 @@
         <x:v>Thanh toán điện tử</x:v>
       </x:c>
       <x:c r="C25" s="12" t="str">
-        <x:v>TC-CAB-024, TC-CAB-048</x:v>
+        <x:v>TC-CAB-016</x:v>
       </x:c>
       <x:c r="D25" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2277,10 +1756,10 @@
         <x:v>Xử lý thanh toán thất bại</x:v>
       </x:c>
       <x:c r="C26" s="12" t="str">
-        <x:v>TC-CAB-025, TC-CAB-048</x:v>
+        <x:v>TC-CAB-017</x:v>
       </x:c>
       <x:c r="D26" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2294,10 +1773,10 @@
         <x:v>Thông báo đặt xe</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>TC-CAB-026, TC-CAB-042, TC-CAB-045</x:v>
+        <x:v>TC-CAB-003, TC-CAB-007, TC-CAB-010, TC-CAB-018</x:v>
       </x:c>
       <x:c r="D27" s="13" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2311,10 +1790,10 @@
         <x:v>Thông báo cho tài xế</x:v>
       </x:c>
       <x:c r="C28" s="12" t="str">
-        <x:v>TC-CAB-027, TC-CAB-043</x:v>
+        <x:v>TC-CAB-006, TC-CAB-008, TC-CAB-009, TC-CAB-018</x:v>
       </x:c>
       <x:c r="D28" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E28" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2328,10 +1807,10 @@
         <x:v>Thông báo trạng thái chuyến</x:v>
       </x:c>
       <x:c r="C29" s="12" t="str">
-        <x:v>TC-CAB-028, TC-CAB-042, TC-CAB-046</x:v>
+        <x:v>TC-CAB-013, TC-CAB-019</x:v>
       </x:c>
       <x:c r="D29" s="13" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E29" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2345,7 +1824,7 @@
         <x:v>Thông báo thanh toán</x:v>
       </x:c>
       <x:c r="C30" s="12" t="str">
-        <x:v>TC-CAB-029, TC-CAB-047, TC-CAB-048</x:v>
+        <x:v>TC-CAB-015, TC-CAB-016, TC-CAB-017</x:v>
       </x:c>
       <x:c r="D30" s="13" t="n">
         <x:v>3</x:v>
@@ -2362,7 +1841,7 @@
         <x:v>Quản lý khách hàng</x:v>
       </x:c>
       <x:c r="C31" s="12" t="str">
-        <x:v>TC-CAB-030, TC-CAB-049</x:v>
+        <x:v>TC-CAB-020, TC-CAB-030</x:v>
       </x:c>
       <x:c r="D31" s="13" t="n">
         <x:v>2</x:v>
@@ -2379,7 +1858,7 @@
         <x:v>Quản lý tài xế</x:v>
       </x:c>
       <x:c r="C32" s="12" t="str">
-        <x:v>TC-CAB-031, TC-CAB-049</x:v>
+        <x:v>TC-CAB-021, TC-CAB-030</x:v>
       </x:c>
       <x:c r="D32" s="13" t="n">
         <x:v>2</x:v>
@@ -2396,7 +1875,7 @@
         <x:v>Quản lý phương tiện</x:v>
       </x:c>
       <x:c r="C33" s="12" t="str">
-        <x:v>TC-CAB-032, TC-CAB-049</x:v>
+        <x:v>TC-CAB-021, TC-CAB-030</x:v>
       </x:c>
       <x:c r="D33" s="13" t="n">
         <x:v>2</x:v>
@@ -2413,7 +1892,7 @@
         <x:v>Giám sát chuyến đi</x:v>
       </x:c>
       <x:c r="C34" s="12" t="str">
-        <x:v>TC-CAB-033</x:v>
+        <x:v>TC-CAB-022</x:v>
       </x:c>
       <x:c r="D34" s="13" t="n">
         <x:v>1</x:v>
@@ -2430,7 +1909,7 @@
         <x:v>Xử lý sự cố</x:v>
       </x:c>
       <x:c r="C35" s="12" t="str">
-        <x:v>TC-CAB-034</x:v>
+        <x:v>TC-CAB-023</x:v>
       </x:c>
       <x:c r="D35" s="13" t="n">
         <x:v>1</x:v>
@@ -2447,7 +1926,7 @@
         <x:v>Tra cứu giao dịch</x:v>
       </x:c>
       <x:c r="C36" s="12" t="str">
-        <x:v>TC-CAB-035</x:v>
+        <x:v>TC-CAB-024</x:v>
       </x:c>
       <x:c r="D36" s="13" t="n">
         <x:v>1</x:v>
@@ -2464,7 +1943,7 @@
         <x:v>Phân quyền</x:v>
       </x:c>
       <x:c r="C37" s="12" t="str">
-        <x:v>TC-CAB-036, TC-CAB-049</x:v>
+        <x:v>TC-CAB-025, TC-CAB-030</x:v>
       </x:c>
       <x:c r="D37" s="13" t="n">
         <x:v>2</x:v>
@@ -2481,7 +1960,7 @@
         <x:v>Đánh giá tài xế</x:v>
       </x:c>
       <x:c r="C38" s="12" t="str">
-        <x:v>TC-CAB-037, TC-CAB-050</x:v>
+        <x:v>TC-CAB-026, TC-CAB-027</x:v>
       </x:c>
       <x:c r="D38" s="13" t="n">
         <x:v>2</x:v>
@@ -2498,10 +1977,10 @@
         <x:v>Lịch sử chuyến</x:v>
       </x:c>
       <x:c r="C39" s="12" t="str">
-        <x:v>TC-CAB-038, TC-CAB-050</x:v>
+        <x:v>TC-CAB-028</x:v>
       </x:c>
       <x:c r="D39" s="13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E39" s="13" t="str">
         <x:v>Covered</x:v>
@@ -2515,7 +1994,7 @@
         <x:v>Báo cáo hoạt động</x:v>
       </x:c>
       <x:c r="C40" s="12" t="str">
-        <x:v>TC-CAB-039</x:v>
+        <x:v>TC-CAB-029</x:v>
       </x:c>
       <x:c r="D40" s="13" t="n">
         <x:v>1</x:v>
@@ -2527,68 +2006,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb36c613374dd4068"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcb061301c154533"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="11" t="str">
-        <x:v>Mục</x:v>
-      </x:c>
-      <x:c r="B1" s="11" t="str">
-        <x:v>Nội dung</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>Nguồn</x:v>
-      </x:c>
-      <x:c r="B2" s="12" t="str">
-        <x:v>SRS CAB: Functional Requirements FR01–FR39.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="38" customHeight="1">
-      <x:c r="A3" s="12" t="str">
-        <x:v>Phạm vi</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>Đã rút gọn còn đúng 50 test case; ưu tiên case cốt lõi theo từng FR và các luồng lỗi/rủi ro quan trọng.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="38" customHeight="1">
-      <x:c r="A4" s="12" t="str">
-        <x:v>Nguyên tắc</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="str">
-        <x:v>Gộp các luồng liên quan để tránh trùng lặp, không tạo thêm yêu cầu ngoài SRS.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="38" customHeight="1">
-      <x:c r="A5" s="12" t="str">
-        <x:v>Truy vết</x:v>
-      </x:c>
-      <x:c r="B5" s="12" t="str">
-        <x:v>Sheet FR Traceability liệt kê chính xác mọi Test Case ID đang còn lại cho từng FR.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="38" customHeight="1">
-      <x:c r="A6" s="12" t="str">
-        <x:v>Ghi chú</x:v>
-      </x:c>
-      <x:c r="B6" s="12" t="str">
-        <x:v>Các quy tắc chưa được SRS chốt theo chính sách doanh nghiệp được kiểm thử ở mức hành vi được nêu trong SRS.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>